--- a/Result/profitability/3164.xlsx
+++ b/Result/profitability/3164.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1425</v>
+        <v>0.15625</v>
       </c>
       <c r="N2" t="n">
-        <v>62.5675</v>
+        <v>62.19499999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.18875</v>
+        <v>0.20875</v>
       </c>
       <c r="N3" t="n">
-        <v>65.14999999999999</v>
+        <v>66.10875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.18625</v>
+        <v>0.185</v>
       </c>
       <c r="N4" t="n">
-        <v>68.84999999999999</v>
+        <v>68.375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2075</v>
+        <v>0.2425</v>
       </c>
       <c r="N5" t="n">
-        <v>72.16249999999999</v>
+        <v>71.65625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1139,10 +1139,10 @@
         <v>0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24875</v>
+        <v>0.235</v>
       </c>
       <c r="N6" t="n">
-        <v>74.8925</v>
+        <v>74.4825</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1266,10 +1266,10 @@
         <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26625</v>
+        <v>0.2525</v>
       </c>
       <c r="N7" t="n">
-        <v>77.45125</v>
+        <v>77.06375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.27625</v>
+        <v>0.2925</v>
       </c>
       <c r="N8" t="n">
-        <v>79.29875</v>
+        <v>79.93125000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1649,7 +1649,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4425</v>
+        <v>0.4424999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>81.55875</v>
@@ -1776,7 +1776,7 @@
         <v>0.72</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4775</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>81.20125</v>
@@ -1903,7 +1903,7 @@
         <v>0.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0.53625</v>
+        <v>0.5362499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>80.03125</v>
@@ -2033,7 +2033,7 @@
         <v>0.5862499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>78.46000000000001</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3164</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>103</v>
+      </c>
+      <c r="D75" t="n">
+        <v>42</v>
+      </c>
+      <c r="E75" t="n">
+        <v>61</v>
+      </c>
+      <c r="F75" t="n">
+        <v>59.14</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.12375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.060000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09356508875739644</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.049999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06409241968665924</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
